--- a/01_electrical/02_stm32cubemx_basic/05_test_uart/test_uart.xlsx
+++ b/01_electrical/02_stm32cubemx_basic/05_test_uart/test_uart.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Organization\1_RoboWalker\Admin\train\main\01_electrical\02_stm32cubemx_basic\05_test_uart\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18E56D56-BD05-4C81-9BA1-1154111F3675}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C7FE637-D871-4862-AB8C-7E4C60FDEB09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{440ED87A-7A11-465C-AD38-6898698AFA1E}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{440ED87A-7A11-465C-AD38-6898698AFA1E}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
   <si>
     <t>分段</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -96,6 +96,10 @@
   <si>
     <t>链路上不传输任何信息
 必须为高电平1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0~1</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -211,14 +215,14 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -550,10 +554,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:1023 1026:2046 2049:3072 3075:4095 4098:5118 5121:6144 6147:7167 7170:8190 8193:9216 9219:10239 10242:11262 11265:12288 12291:13311 13314:14334 14337:15360 15363:16383" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="B1" s="8"/>
+      <c r="B1" s="10"/>
     </row>
     <row r="2" spans="1:1023 1026:2046 2049:3072 3075:4095 4098:5118 5121:6144 6147:7167 7170:8190 8193:9216 9219:10239 10242:11262 11265:12288 12291:13311 13314:14334 14337:15360 15363:16383" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A2" s="3" t="s">
@@ -573,7 +577,7 @@
       <c r="B3" s="4">
         <v>1</v>
       </c>
-      <c r="C3" s="9" t="s">
+      <c r="C3" s="8" t="s">
         <v>12</v>
       </c>
     </row>
@@ -584,7 +588,7 @@
       <c r="B4" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="C4" s="10" t="s">
+      <c r="C4" s="9" t="s">
         <v>13</v>
       </c>
     </row>
@@ -592,8 +596,8 @@
       <c r="A5" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="4">
-        <v>1</v>
+      <c r="B5" s="4" t="s">
+        <v>16</v>
       </c>
       <c r="C5" s="4" t="s">
         <v>11</v>
@@ -6066,7 +6070,7 @@
       <c r="B6" s="5">
         <v>1</v>
       </c>
-      <c r="C6" s="10" t="s">
+      <c r="C6" s="9" t="s">
         <v>14</v>
       </c>
     </row>
@@ -6077,7 +6081,7 @@
       <c r="B7" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="C7" s="9" t="s">
+      <c r="C7" s="8" t="s">
         <v>15</v>
       </c>
       <c r="F7" s="1"/>
@@ -11547,5 +11551,6 @@
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>